--- a/checklists/excel/techlead/architecture.xlsx
+++ b/checklists/excel/techlead/architecture.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Architecture" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Architecture Review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,72 +425,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item Text</t>
+          <t>Sr.No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Main Category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Sub Category</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>How to Measure</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Follows microservices/component boundaries (MUST)</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>Architecture Review</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Service boundaries respected; Inter-service communication proper; Data ownership clear</t>
+          <t>Verify scalability considerations</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Code should respect established service and component boundaries</t>
+          <t>Ensure the architecture can handle expected load and can be scaled horizontally or vertically as needed.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Implements caching, connection pooling, and load balancing</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Performance testing and load testing</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Database design is appropriate (GOOD)</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>Architecture Review</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Normalization level appropriate; Indexes optimized; Migration strategy planned</t>
+          <t>Check security implementation</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Database design should support the application requirements efficiently</t>
+          <t>Verify that security measures are properly implemented including authentication, authorization, and data protection.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Uses OAuth2, JWT, encryption, and secure communication</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Security audit and penetration testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Architecture Review</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Validate database design</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ensure database schema is properly normalized and optimized for the application requirements.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Follows database normalization rules and uses appropriate indexes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Database performance analysis and query optimization</t>
         </is>
       </c>
     </row>
